--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260713.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260713.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>85,664,929</t>
+          <t>85,766,177</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>4.50%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>444,919,884</t>
+          <t>445,447,660</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>4.12%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>170,322,681</t>
+          <t>171,858,369</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>4.16%</t>
+          <t>3.99%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>66,600,335</t>
+          <t>67,313,183</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>3.96%</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>706,255,505</t>
+          <t>706,777,325</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -721,34 +721,34 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>680,597,909</t>
+          <t>681,414,549</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.69%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>161,440,773</t>
+          <t>129,434,693</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.59%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>536,595,412</t>
+          <t>537,233,140</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.51%</t>
         </is>
       </c>
     </row>
@@ -787,122 +787,122 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>34,146,096</t>
+          <t>34,186,896</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>160,651,095</t>
+          <t>153,147,261</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.27%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>121,977,114</t>
+          <t>161,487,783</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>25,234,753</t>
+          <t>290,480,437</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>290,130,997</t>
+          <t>248,558,344</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>248,274,440</t>
+          <t>25,266,561</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>92,180,858</t>
+          <t>92,291,578</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>586,675,196</t>
+          <t>587,373,724</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
@@ -963,139 +963,139 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>466,085,173</t>
+          <t>475,517,005</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>67,327,026</t>
+          <t>73,980,946</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>73,893,618</t>
+          <t>1,784</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>23,108,207</t>
+          <t>67,404,722</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>28,153,535</t>
+          <t>140,468,187</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>140,299,291</t>
+          <t>429,134,313</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>428,621,673</t>
+          <t>22,129,591</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1117,34 +1117,34 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>146,261,430</t>
+          <t>152,023,918</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>3,347,364</t>
+          <t>28,187,519</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -1161,34 +1161,34 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>62,033,654</t>
+          <t>62,108,022</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>35,590,989</t>
+          <t>3,215,428</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
@@ -1205,73 +1205,73 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>25,341,677</t>
+          <t>25,371,021</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>161,953,540</t>
+          <t>35,633,549</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,173</t>
+          <t>31,508,773</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>31,471,365</t>
+          <t>162,149,668</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1293,34 +1293,34 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>123,366,272</t>
+          <t>123,508,160</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,084</t>
+          <t>249,234,325</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>32,105,652</t>
+          <t>32,144,948</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,127 +1349,127 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>248,932,725</t>
+          <t>211,791,457</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>211,534,849</t>
+          <t>75,519,842</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>75,426,082</t>
+          <t>198,838,842</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>198,595,514</t>
+          <t>80,773,039</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>80,674,991</t>
+          <t>22,951,395</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>22,922,979</t>
+          <t>39,739,702</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,88 +1481,88 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>39,691,542</t>
+          <t>146,565,038</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>146,381,582</t>
+          <t>26,068,234</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>26,040,426</t>
+          <t>148,713,844</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>148,532,820</t>
+          <t>473</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>134,771,543</t>
+          <t>134,939,415</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>105,359,574</t>
+          <t>105,490,934</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>23,188,099</t>
+          <t>23,214,211</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>33,618,859</t>
+          <t>33,661,611</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>11,080,051</t>
+          <t>11,094,163</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,44 +1679,44 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>13,525,655</t>
+          <t>29,300,192</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>29,263,616</t>
+          <t>13,546,442</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>108,316,296</t>
+          <t>108,454,856</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
